--- a/Shiny/Datos limpios/pricing_diario_historico_cebada.xlsx
+++ b/Shiny/Datos limpios/pricing_diario_historico_cebada.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K2919"/>
+  <dimension ref="A1:K2938"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -108352,33 +108352,736 @@
         <v>45957</v>
       </c>
       <c r="B2919">
+        <v>7856.26</v>
+      </c>
+      <c r="C2919">
+        <v>0</v>
+      </c>
+      <c r="D2919">
+        <v>0</v>
+      </c>
+      <c r="E2919">
+        <v>7856.26</v>
+      </c>
+      <c r="F2919">
+        <v>11532.08</v>
+      </c>
+      <c r="G2919">
+        <v>0</v>
+      </c>
+      <c r="H2919">
+        <v>0</v>
+      </c>
+      <c r="I2919">
+        <v>11532.08</v>
+      </c>
+      <c r="J2919">
+        <v>19388.34</v>
+      </c>
+      <c r="K2919" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2920">
+      <c r="A2920" s="2">
+        <v>45958</v>
+      </c>
+      <c r="B2920">
+        <v>10205.26</v>
+      </c>
+      <c r="C2920">
+        <v>0</v>
+      </c>
+      <c r="D2920">
+        <v>0</v>
+      </c>
+      <c r="E2920">
+        <v>10205.26</v>
+      </c>
+      <c r="F2920">
+        <v>8016</v>
+      </c>
+      <c r="G2920">
+        <v>0</v>
+      </c>
+      <c r="H2920">
+        <v>0</v>
+      </c>
+      <c r="I2920">
+        <v>8016</v>
+      </c>
+      <c r="J2920">
+        <v>18221.26</v>
+      </c>
+      <c r="K2920" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2921">
+      <c r="A2921" s="2">
+        <v>45959</v>
+      </c>
+      <c r="B2921">
+        <v>10783</v>
+      </c>
+      <c r="C2921">
+        <v>1030</v>
+      </c>
+      <c r="D2921">
+        <v>340</v>
+      </c>
+      <c r="E2921">
+        <v>11473</v>
+      </c>
+      <c r="F2921">
+        <v>300</v>
+      </c>
+      <c r="G2921">
+        <v>0</v>
+      </c>
+      <c r="H2921">
+        <v>0</v>
+      </c>
+      <c r="I2921">
+        <v>300</v>
+      </c>
+      <c r="J2921">
+        <v>11773</v>
+      </c>
+      <c r="K2921" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2922">
+      <c r="A2922" s="2">
+        <v>45960</v>
+      </c>
+      <c r="B2922">
+        <v>18056.23</v>
+      </c>
+      <c r="C2922">
+        <v>0</v>
+      </c>
+      <c r="D2922">
+        <v>0</v>
+      </c>
+      <c r="E2922">
+        <v>18056.23</v>
+      </c>
+      <c r="F2922">
+        <v>3480</v>
+      </c>
+      <c r="G2922">
+        <v>0</v>
+      </c>
+      <c r="H2922">
+        <v>0</v>
+      </c>
+      <c r="I2922">
+        <v>3480</v>
+      </c>
+      <c r="J2922">
+        <v>21536.23</v>
+      </c>
+      <c r="K2922" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2923">
+      <c r="A2923" s="2">
+        <v>45961</v>
+      </c>
+      <c r="B2923">
+        <v>30580</v>
+      </c>
+      <c r="C2923">
+        <v>0</v>
+      </c>
+      <c r="D2923">
+        <v>150</v>
+      </c>
+      <c r="E2923">
+        <v>30430</v>
+      </c>
+      <c r="F2923">
+        <v>930</v>
+      </c>
+      <c r="G2923">
+        <v>0</v>
+      </c>
+      <c r="H2923">
+        <v>0</v>
+      </c>
+      <c r="I2923">
+        <v>930</v>
+      </c>
+      <c r="J2923">
+        <v>31360</v>
+      </c>
+      <c r="K2923" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2924">
+      <c r="A2924" s="2">
+        <v>45964</v>
+      </c>
+      <c r="B2924">
+        <v>26005.8</v>
+      </c>
+      <c r="C2924">
+        <v>0</v>
+      </c>
+      <c r="D2924">
+        <v>0</v>
+      </c>
+      <c r="E2924">
+        <v>26005.8</v>
+      </c>
+      <c r="F2924">
         <v>450</v>
       </c>
-      <c r="C2919">
-        <v>0</v>
-      </c>
-      <c r="D2919">
-        <v>0</v>
-      </c>
-      <c r="E2919">
+      <c r="G2924">
+        <v>0</v>
+      </c>
+      <c r="H2924">
+        <v>0</v>
+      </c>
+      <c r="I2924">
         <v>450</v>
       </c>
-      <c r="F2919">
-        <v>7500</v>
-      </c>
-      <c r="G2919">
-        <v>0</v>
-      </c>
-      <c r="H2919">
-        <v>0</v>
-      </c>
-      <c r="I2919">
-        <v>7500</v>
-      </c>
-      <c r="J2919">
-        <v>7950</v>
-      </c>
-      <c r="K2919" t="inlineStr">
+      <c r="J2924">
+        <v>26455.8</v>
+      </c>
+      <c r="K2924" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2925">
+      <c r="A2925" s="2">
+        <v>45965</v>
+      </c>
+      <c r="B2925">
+        <v>8770</v>
+      </c>
+      <c r="C2925">
+        <v>0</v>
+      </c>
+      <c r="D2925">
+        <v>0</v>
+      </c>
+      <c r="E2925">
+        <v>8770</v>
+      </c>
+      <c r="F2925">
+        <v>32590.76</v>
+      </c>
+      <c r="G2925">
+        <v>0</v>
+      </c>
+      <c r="H2925">
+        <v>0</v>
+      </c>
+      <c r="I2925">
+        <v>32590.76</v>
+      </c>
+      <c r="J2925">
+        <v>41360.75999999999</v>
+      </c>
+      <c r="K2925" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2926">
+      <c r="A2926" s="2">
+        <v>45966</v>
+      </c>
+      <c r="B2926">
+        <v>20645.77</v>
+      </c>
+      <c r="C2926">
+        <v>0</v>
+      </c>
+      <c r="D2926">
+        <v>0</v>
+      </c>
+      <c r="E2926">
+        <v>20645.77</v>
+      </c>
+      <c r="F2926">
+        <v>27.88</v>
+      </c>
+      <c r="G2926">
+        <v>0</v>
+      </c>
+      <c r="H2926">
+        <v>0</v>
+      </c>
+      <c r="I2926">
+        <v>27.88</v>
+      </c>
+      <c r="J2926">
+        <v>20673.65</v>
+      </c>
+      <c r="K2926" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2927">
+      <c r="A2927" s="2">
+        <v>45967</v>
+      </c>
+      <c r="B2927">
+        <v>12972.76</v>
+      </c>
+      <c r="C2927">
+        <v>0</v>
+      </c>
+      <c r="D2927">
+        <v>2000</v>
+      </c>
+      <c r="E2927">
+        <v>10972.76</v>
+      </c>
+      <c r="F2927">
+        <v>1320</v>
+      </c>
+      <c r="G2927">
+        <v>0</v>
+      </c>
+      <c r="H2927">
+        <v>0</v>
+      </c>
+      <c r="I2927">
+        <v>1320</v>
+      </c>
+      <c r="J2927">
+        <v>12292.76</v>
+      </c>
+      <c r="K2927" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2928">
+      <c r="A2928" s="2">
+        <v>45968</v>
+      </c>
+      <c r="B2928">
+        <v>16406.74</v>
+      </c>
+      <c r="C2928">
+        <v>0</v>
+      </c>
+      <c r="D2928">
+        <v>0</v>
+      </c>
+      <c r="E2928">
+        <v>16406.74</v>
+      </c>
+      <c r="F2928">
+        <v>7378.32</v>
+      </c>
+      <c r="G2928">
+        <v>0</v>
+      </c>
+      <c r="H2928">
+        <v>0</v>
+      </c>
+      <c r="I2928">
+        <v>7378.32</v>
+      </c>
+      <c r="J2928">
+        <v>23785.06</v>
+      </c>
+      <c r="K2928" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2929">
+      <c r="A2929" s="2">
+        <v>45971</v>
+      </c>
+      <c r="B2929">
+        <v>14869.99</v>
+      </c>
+      <c r="C2929">
+        <v>60</v>
+      </c>
+      <c r="D2929">
+        <v>280</v>
+      </c>
+      <c r="E2929">
+        <v>14649.99</v>
+      </c>
+      <c r="F2929">
+        <v>150</v>
+      </c>
+      <c r="G2929">
+        <v>0</v>
+      </c>
+      <c r="H2929">
+        <v>0</v>
+      </c>
+      <c r="I2929">
+        <v>150</v>
+      </c>
+      <c r="J2929">
+        <v>14799.99</v>
+      </c>
+      <c r="K2929" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2930">
+      <c r="A2930" s="2">
+        <v>45972</v>
+      </c>
+      <c r="B2930">
+        <v>21980.6</v>
+      </c>
+      <c r="C2930">
+        <v>0</v>
+      </c>
+      <c r="D2930">
+        <v>0</v>
+      </c>
+      <c r="E2930">
+        <v>21980.6</v>
+      </c>
+      <c r="F2930">
+        <v>80</v>
+      </c>
+      <c r="G2930">
+        <v>0</v>
+      </c>
+      <c r="H2930">
+        <v>0</v>
+      </c>
+      <c r="I2930">
+        <v>80</v>
+      </c>
+      <c r="J2930">
+        <v>22060.6</v>
+      </c>
+      <c r="K2930" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2931">
+      <c r="A2931" s="2">
+        <v>45973</v>
+      </c>
+      <c r="B2931">
+        <v>10611.56</v>
+      </c>
+      <c r="C2931">
+        <v>0</v>
+      </c>
+      <c r="D2931">
+        <v>130</v>
+      </c>
+      <c r="E2931">
+        <v>10481.56</v>
+      </c>
+      <c r="F2931">
+        <v>0</v>
+      </c>
+      <c r="G2931">
+        <v>0</v>
+      </c>
+      <c r="H2931">
+        <v>0</v>
+      </c>
+      <c r="I2931">
+        <v>0</v>
+      </c>
+      <c r="J2931">
+        <v>10481.56</v>
+      </c>
+      <c r="K2931" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2932">
+      <c r="A2932" s="2">
+        <v>45974</v>
+      </c>
+      <c r="B2932">
+        <v>15739.25</v>
+      </c>
+      <c r="C2932">
+        <v>0</v>
+      </c>
+      <c r="D2932">
+        <v>0</v>
+      </c>
+      <c r="E2932">
+        <v>15739.25</v>
+      </c>
+      <c r="F2932">
+        <v>0</v>
+      </c>
+      <c r="G2932">
+        <v>0</v>
+      </c>
+      <c r="H2932">
+        <v>0</v>
+      </c>
+      <c r="I2932">
+        <v>0</v>
+      </c>
+      <c r="J2932">
+        <v>15739.25</v>
+      </c>
+      <c r="K2932" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2933">
+      <c r="A2933" s="2">
+        <v>45975</v>
+      </c>
+      <c r="B2933">
+        <v>12582.57</v>
+      </c>
+      <c r="C2933">
+        <v>2000</v>
+      </c>
+      <c r="D2933">
+        <v>0</v>
+      </c>
+      <c r="E2933">
+        <v>14582.57</v>
+      </c>
+      <c r="F2933">
+        <v>40</v>
+      </c>
+      <c r="G2933">
+        <v>0</v>
+      </c>
+      <c r="H2933">
+        <v>0</v>
+      </c>
+      <c r="I2933">
+        <v>40</v>
+      </c>
+      <c r="J2933">
+        <v>14622.57</v>
+      </c>
+      <c r="K2933" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2934">
+      <c r="A2934" s="2">
+        <v>45978</v>
+      </c>
+      <c r="B2934">
+        <v>17610.74</v>
+      </c>
+      <c r="C2934">
+        <v>0</v>
+      </c>
+      <c r="D2934">
+        <v>60</v>
+      </c>
+      <c r="E2934">
+        <v>17550.74</v>
+      </c>
+      <c r="F2934">
+        <v>14198</v>
+      </c>
+      <c r="G2934">
+        <v>0</v>
+      </c>
+      <c r="H2934">
+        <v>0</v>
+      </c>
+      <c r="I2934">
+        <v>14198</v>
+      </c>
+      <c r="J2934">
+        <v>31748.74</v>
+      </c>
+      <c r="K2934" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2935">
+      <c r="A2935" s="2">
+        <v>45979</v>
+      </c>
+      <c r="B2935">
+        <v>28003.37</v>
+      </c>
+      <c r="C2935">
+        <v>0</v>
+      </c>
+      <c r="D2935">
+        <v>1000</v>
+      </c>
+      <c r="E2935">
+        <v>27003.37</v>
+      </c>
+      <c r="F2935">
+        <v>420</v>
+      </c>
+      <c r="G2935">
+        <v>0</v>
+      </c>
+      <c r="H2935">
+        <v>0</v>
+      </c>
+      <c r="I2935">
+        <v>420</v>
+      </c>
+      <c r="J2935">
+        <v>27423.37</v>
+      </c>
+      <c r="K2935" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2936">
+      <c r="A2936" s="2">
+        <v>45980</v>
+      </c>
+      <c r="B2936">
+        <v>25271</v>
+      </c>
+      <c r="C2936">
+        <v>0</v>
+      </c>
+      <c r="D2936">
+        <v>0</v>
+      </c>
+      <c r="E2936">
+        <v>25271</v>
+      </c>
+      <c r="F2936">
+        <v>1785</v>
+      </c>
+      <c r="G2936">
+        <v>0</v>
+      </c>
+      <c r="H2936">
+        <v>0</v>
+      </c>
+      <c r="I2936">
+        <v>1785</v>
+      </c>
+      <c r="J2936">
+        <v>27056</v>
+      </c>
+      <c r="K2936" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2937">
+      <c r="A2937" s="2">
+        <v>45981</v>
+      </c>
+      <c r="B2937">
+        <v>26505.74</v>
+      </c>
+      <c r="C2937">
+        <v>2200</v>
+      </c>
+      <c r="D2937">
+        <v>300</v>
+      </c>
+      <c r="E2937">
+        <v>28405.74</v>
+      </c>
+      <c r="F2937">
+        <v>1010</v>
+      </c>
+      <c r="G2937">
+        <v>0</v>
+      </c>
+      <c r="H2937">
+        <v>0</v>
+      </c>
+      <c r="I2937">
+        <v>1010</v>
+      </c>
+      <c r="J2937">
+        <v>29415.74</v>
+      </c>
+      <c r="K2937" t="inlineStr">
+        <is>
+          <t>CEBADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2938">
+      <c r="A2938" s="2">
+        <v>45982</v>
+      </c>
+      <c r="B2938">
+        <v>10210</v>
+      </c>
+      <c r="C2938">
+        <v>0</v>
+      </c>
+      <c r="D2938">
+        <v>0</v>
+      </c>
+      <c r="E2938">
+        <v>10210</v>
+      </c>
+      <c r="F2938">
+        <v>0</v>
+      </c>
+      <c r="G2938">
+        <v>0</v>
+      </c>
+      <c r="H2938">
+        <v>0</v>
+      </c>
+      <c r="I2938">
+        <v>0</v>
+      </c>
+      <c r="J2938">
+        <v>10210</v>
+      </c>
+      <c r="K2938" t="inlineStr">
         <is>
           <t>CEBADA</t>
         </is>
